--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\dobymyself\cms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4D9B81-630B-41FB-A2A8-EA05DAC28D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A997C5E-7AFC-4E99-95BE-5446ED1EFA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -106,14 +106,14 @@
     <t>Email</t>
   </si>
   <si>
-    <t>mahfuja.toma@oculintech.com</t>
+    <t>mahfujatoma5431@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +144,14 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -193,10 +201,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -226,8 +235,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -663,7 +676,7 @@
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -751,7 +764,7 @@
       <c r="C14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -863,7 +876,7 @@
       <c r="C23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -963,7 +976,7 @@
       <c r="C31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1063,7 +1076,7 @@
       <c r="C39" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1163,7 +1176,7 @@
       <c r="C47" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1263,7 +1276,7 @@
       <c r="C55" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1364,7 +1377,7 @@
       <c r="C63" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1458,7 +1471,7 @@
       <c r="C71" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1552,7 +1565,7 @@
       <c r="C79" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1646,7 +1659,7 @@
       <c r="C87" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="10" t="s">
+      <c r="D87" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1740,7 +1753,7 @@
       <c r="C95" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1834,7 +1847,7 @@
       <c r="C103" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1928,7 +1941,7 @@
       <c r="C111" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D111" s="10" t="s">
+      <c r="D111" s="11" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2022,7 +2035,7 @@
       <c r="C119" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="11" t="s">
         <v>21</v>
       </c>
     </row>

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A997C5E-7AFC-4E99-95BE-5446ED1EFA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA124E-4F35-4987-A80A-70F5AAD34A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -649,7 +649,9 @@
       <c r="C5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
@@ -726,9 +728,7 @@
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D11" s="10"/>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
@@ -752,7 +752,9 @@
       <c r="C13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="7"/>
+      <c r="D13" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
@@ -802,9 +804,7 @@
       <c r="C17" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
@@ -852,7 +852,9 @@
       <c r="C21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="7"/>
+      <c r="D21" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
@@ -902,9 +904,7 @@
       <c r="C25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
@@ -952,7 +952,9 @@
       <c r="C29" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="7"/>
+      <c r="D29" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
@@ -1002,9 +1004,7 @@
       <c r="C33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
@@ -1052,7 +1052,9 @@
       <c r="C37" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="7"/>
+      <c r="D37" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
@@ -1102,9 +1104,7 @@
       <c r="C41" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D41" s="10"/>
     </row>
     <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
@@ -1152,7 +1152,9 @@
       <c r="C45" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="7"/>
+      <c r="D45" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
@@ -1202,9 +1204,7 @@
       <c r="C49" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D49" s="10"/>
     </row>
     <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
@@ -1252,7 +1252,9 @@
       <c r="C53" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="7"/>
+      <c r="D53" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
@@ -1302,9 +1304,7 @@
       <c r="C57" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D57" s="10"/>
     </row>
     <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
@@ -1340,9 +1340,7 @@
       <c r="C60" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D60" s="10"/>
     </row>
     <row r="61" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
@@ -1391,6 +1389,9 @@
       <c r="C64" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D64" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="65" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
@@ -1402,9 +1403,7 @@
       <c r="C65" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D65" s="10"/>
     </row>
     <row r="66" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
@@ -1449,6 +1448,9 @@
       <c r="C69" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D69" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="70" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
@@ -1496,9 +1498,7 @@
       <c r="C73" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D73" s="10"/>
     </row>
     <row r="74" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
@@ -1543,6 +1543,9 @@
       <c r="C77" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D77" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="78" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
@@ -1590,9 +1593,7 @@
       <c r="C81" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D81" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D81" s="10"/>
     </row>
     <row r="82" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
@@ -1637,6 +1638,9 @@
       <c r="C85" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D85" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="86" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
@@ -1684,9 +1688,7 @@
       <c r="C89" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D89" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D89" s="10"/>
     </row>
     <row r="90" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
@@ -1731,6 +1733,9 @@
       <c r="C93" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D93" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="94" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
@@ -1778,9 +1783,7 @@
       <c r="C97" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D97" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D97" s="10"/>
     </row>
     <row r="98" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
@@ -1825,6 +1828,9 @@
       <c r="C101" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D101" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="102" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
@@ -1872,9 +1878,7 @@
       <c r="C105" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D105" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D105" s="10"/>
     </row>
     <row r="106" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
@@ -1919,6 +1923,9 @@
       <c r="C109" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D109" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="110" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
@@ -1966,9 +1973,7 @@
       <c r="C113" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D113" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D113" s="10"/>
     </row>
     <row r="114" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
@@ -2013,6 +2018,9 @@
       <c r="C117" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="D117" s="11" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="118" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
@@ -2060,14 +2068,29 @@
       <c r="C121" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D121" s="10" t="s">
-        <v>19</v>
-      </c>
+      <c r="D121" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:C123" xr:uid="{E1FB5C3E-D482-484D-8C71-32C481BF75DA}"/>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{73965210-AF45-434C-9997-EC4B858A4516}"/>
+    <hyperlink ref="D13" r:id="rId2" xr:uid="{2EC4AA29-8667-4F84-B863-E12F9B084B44}"/>
+    <hyperlink ref="D21" r:id="rId3" xr:uid="{DDD0733A-C40D-4D69-B665-B30AC3905495}"/>
+    <hyperlink ref="D29" r:id="rId4" xr:uid="{F612D8E7-14B3-4399-8D85-AE62FC872E0E}"/>
+    <hyperlink ref="D37" r:id="rId5" xr:uid="{26E9E5BB-55EE-45F3-85A2-F0B8242537E8}"/>
+    <hyperlink ref="D45" r:id="rId6" xr:uid="{EE20484F-9F2C-42FA-A3FD-49FF2377B553}"/>
+    <hyperlink ref="D53" r:id="rId7" xr:uid="{EB3A445B-F0B1-4834-B366-B7987C8BC0AD}"/>
+    <hyperlink ref="D64" r:id="rId8" xr:uid="{945E9506-F6A7-4019-B526-725709DEE254}"/>
+    <hyperlink ref="D69" r:id="rId9" xr:uid="{65E026CE-5919-4DBC-AE06-D8AF53630533}"/>
+    <hyperlink ref="D77" r:id="rId10" xr:uid="{54482943-3E2C-4A82-BB56-0944C6FC9E59}"/>
+    <hyperlink ref="D85" r:id="rId11" xr:uid="{E28CDF9E-7B4B-44E7-A827-AB25D9D857D0}"/>
+    <hyperlink ref="D93" r:id="rId12" xr:uid="{F69F5627-AF07-4ADB-A700-9EF54169BED1}"/>
+    <hyperlink ref="D101" r:id="rId13" xr:uid="{54F77405-0341-4E3B-A268-55EA74B9E5BE}"/>
+    <hyperlink ref="D109" r:id="rId14" xr:uid="{A91F524B-B019-42C3-BC71-79B11E333872}"/>
+    <hyperlink ref="D117" r:id="rId15" xr:uid="{140EBCD1-6BA3-4EC8-B081-B5D598787657}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="17" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="17" orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
 

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA124E-4F35-4987-A80A-70F5AAD34A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8163F917-D9F7-403A-814A-B12A6E6B20D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -106,7 +106,7 @@
     <t>Email</t>
   </si>
   <si>
-    <t>mahfujatoma5431@gmail.com</t>
+    <t>mahfuja.toma@oculintech.com</t>
   </si>
 </sst>
 </file>

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8163F917-D9F7-403A-814A-B12A6E6B20D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F05B191-5983-4F65-A94B-14F6181FF31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F05B191-5983-4F65-A94B-14F6181FF31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A273B510-D8E7-43C9-846D-8D43264FA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>mahfuja.toma@oculintech.com</t>
+  </si>
+  <si>
+    <t>topu.rajbongshi@oculintech.com</t>
   </si>
 </sst>
 </file>
@@ -205,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -222,21 +225,26 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -573,1524 +581,1557 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FB5C3E-D482-484D-8C71-32C481BF75DA}">
-  <dimension ref="A1:J121"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J123"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="2" width="18.109375" customWidth="1"/>
     <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="32.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" style="10" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
         <v>46113</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
         <v>46114</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
         <v>46115</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
         <v>46116</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>46117</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>46117</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="7"/>
       <c r="J6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
         <v>46118</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
         <v>46119</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
         <v>46120</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="D9" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
         <v>46121</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="7">
         <v>46122</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
         <v>46123</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
+      <c r="D12" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
         <v>46124</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>46126</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>46125</v>
-      </c>
-      <c r="B14" s="8" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>46127</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
+        <v>46128</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
+        <v>46129</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="7">
+        <v>46130</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>46131</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="7">
+        <v>46132</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>46133</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="7">
+        <v>46134</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D23" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9">
-        <v>46126</v>
-      </c>
-      <c r="B15" s="8" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
+        <v>46135</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="7">
+        <v>46136</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="7">
+        <v>46137</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="7">
+        <v>46138</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>46139</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>46140</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>46141</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
-        <v>46127</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D30" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>46142</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="7">
+        <v>46143</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="7">
+        <v>46144</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="11"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="7">
+        <v>46145</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="7">
+        <v>46146</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="9">
-        <v>46128</v>
-      </c>
-      <c r="B17" s="8" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="7">
+        <v>46147</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="7">
+        <v>46148</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="7">
+        <v>46149</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="7">
+        <v>46150</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="7">
+        <v>46151</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="7">
+        <v>46152</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
-        <v>46129</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="D41" s="11"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="7">
+        <v>46153</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="7">
+        <v>46154</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="7">
+        <v>46155</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="7">
+        <v>46156</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="7">
+        <v>46157</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C46" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="7">
+        <v>46158</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="7">
+        <v>46159</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="7">
+        <v>46160</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="11"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="7">
+        <v>46161</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
-        <v>46130</v>
-      </c>
-      <c r="B19" s="8" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="7">
+        <v>46162</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="7">
+        <v>46163</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="7">
+        <v>46164</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="7">
+        <v>46165</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C54" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="7">
+        <v>46166</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="7">
+        <v>46167</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="7">
+        <v>46168</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="11"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="7">
+        <v>46169</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="7">
+        <v>46170</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="7">
+        <v>46171</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="11"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="7">
+        <v>46172</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="7">
+        <v>46173</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="12"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="7">
+        <v>46174</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="7">
+        <v>46175</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="7">
+        <v>46176</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="7">
+        <v>46177</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="12"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="7">
+        <v>46178</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>46131</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="D67" s="12"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="7">
+        <v>46179</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="7">
+        <v>46180</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="7">
+        <v>46181</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="7">
+        <v>46182</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="7">
+        <v>46183</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9">
-        <v>46132</v>
-      </c>
-      <c r="B21" s="8" t="s">
+      <c r="D72" s="12"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="7">
+        <v>46184</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="11"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="7">
+        <v>46185</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="12"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="7">
+        <v>46186</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="12"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="7">
+        <v>46187</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="7">
+        <v>46188</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C77" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="7">
+        <v>46189</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
-        <v>46133</v>
-      </c>
-      <c r="B22" s="8" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="7">
+        <v>46190</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="7">
+        <v>46191</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="12"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="7">
+        <v>46192</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="11"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="7">
+        <v>46193</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="12"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="7">
+        <v>46194</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="12"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="7">
+        <v>46195</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="7">
+        <v>46196</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="7">
+        <v>46197</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="9">
-        <v>46134</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="D86" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="7">
+        <v>46198</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D87" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
-        <v>46135</v>
-      </c>
-      <c r="B24" s="8" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="7">
+        <v>46199</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="12"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="7">
+        <v>46200</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D89" s="11"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="7">
+        <v>46201</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="12"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="7">
+        <v>46202</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="12"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="7">
+        <v>46203</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="7">
+        <v>46204</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="7">
+        <v>46205</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C94" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="7">
+        <v>46206</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="7">
+        <v>46207</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="9">
-        <v>46136</v>
-      </c>
-      <c r="B25" s="8" t="s">
+      <c r="D96" s="12"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="7">
+        <v>46208</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="7">
+        <v>46209</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="12"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="7">
+        <v>46210</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="12"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="7">
+        <v>46211</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="7">
+        <v>46212</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D101" s="8"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="7">
+        <v>46213</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C102" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="7">
+        <v>46214</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="7">
+        <v>46215</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="12"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="7">
+        <v>46216</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9">
-        <v>46137</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="D105" s="11"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="7">
+        <v>46217</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="12"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="7">
+        <v>46218</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="12"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="7">
+        <v>46219</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="7">
+        <v>46220</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109" s="8"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="7">
+        <v>46221</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C110" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="7">
+        <v>46222</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="7">
+        <v>46223</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="12"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="7">
+        <v>46224</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" s="11"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="7">
+        <v>46225</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="9">
-        <v>46138</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="D114" s="12"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="7">
+        <v>46226</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="12"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="7">
+        <v>46227</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="7">
+        <v>46228</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="7">
+        <v>46229</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
-        <v>46139</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="C118" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="7">
+        <v>46230</v>
+      </c>
+      <c r="B119" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="9">
-        <v>46140</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="C119" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="7">
+        <v>46231</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
-        <v>46141</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="9">
-        <v>46142</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
-        <v>46143</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="C120" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="9">
-        <v>46144</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="D120" s="12"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="10"/>
-    </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="9">
-        <v>46145</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="9">
-        <v>46146</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="7"/>
-    </row>
-    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="9">
-        <v>46147</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="7"/>
-    </row>
-    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="9">
-        <v>46148</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="9">
-        <v>46149</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="7"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="9">
-        <v>46150</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="9">
-        <v>46151</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="9">
-        <v>46152</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="9">
-        <v>46153</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="9">
-        <v>46154</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="9">
-        <v>46155</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="9">
-        <v>46156</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="9">
-        <v>46157</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="7"/>
-    </row>
-    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="9">
-        <v>46158</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="9">
-        <v>46159</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="9">
-        <v>46160</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="10"/>
-    </row>
-    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="9">
-        <v>46161</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="9">
-        <v>46162</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" s="7"/>
-    </row>
-    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="9">
-        <v>46163</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="7"/>
-    </row>
-    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="9">
-        <v>46164</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="9">
-        <v>46165</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" s="7"/>
-    </row>
-    <row r="55" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="9">
-        <v>46166</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="9">
-        <v>46167</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A57" s="9">
-        <v>46168</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="10"/>
-    </row>
-    <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="9">
-        <v>46169</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="9">
-        <v>46170</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="9">
-        <v>46171</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="10"/>
-    </row>
-    <row r="61" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="9">
-        <v>46172</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="7"/>
-    </row>
-    <row r="62" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="9">
-        <v>46173</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="9">
-        <v>46174</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="9">
-        <v>46175</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="9">
-        <v>46176</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" s="10"/>
-    </row>
-    <row r="66" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="9">
-        <v>46177</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="9">
-        <v>46178</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="9">
-        <v>46179</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="9">
-        <v>46180</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="9">
-        <v>46181</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="9">
-        <v>46182</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="9">
-        <v>46183</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="9">
-        <v>46184</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="10"/>
-    </row>
-    <row r="74" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="9">
-        <v>46185</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="9">
-        <v>46186</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="9">
-        <v>46187</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="9">
-        <v>46188</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="9">
-        <v>46189</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="9">
-        <v>46190</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A80" s="9">
-        <v>46191</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A81" s="9">
-        <v>46192</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="10"/>
-    </row>
-    <row r="82" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="9">
-        <v>46193</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="9">
-        <v>46194</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="9">
-        <v>46195</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="9">
-        <v>46196</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D85" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="9">
-        <v>46197</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A87" s="9">
-        <v>46198</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="9">
-        <v>46199</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="9">
-        <v>46200</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D89" s="10"/>
-    </row>
-    <row r="90" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="9">
-        <v>46201</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="9">
-        <v>46202</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="9">
-        <v>46203</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="9">
-        <v>46204</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="9">
-        <v>46205</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A95" s="9">
-        <v>46206</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A96" s="9">
-        <v>46207</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A97" s="9">
-        <v>46208</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="10"/>
-    </row>
-    <row r="98" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A98" s="9">
-        <v>46209</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A99" s="9">
-        <v>46210</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="9">
-        <v>46211</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A101" s="9">
-        <v>46212</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A102" s="9">
-        <v>46213</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A103" s="9">
-        <v>46214</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A104" s="9">
-        <v>46215</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="9">
-        <v>46216</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D105" s="10"/>
-    </row>
-    <row r="106" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A106" s="9">
-        <v>46217</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A107" s="9">
-        <v>46218</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="9">
-        <v>46219</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="9">
-        <v>46220</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A110" s="9">
-        <v>46221</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A111" s="9">
-        <v>46222</v>
-      </c>
-      <c r="B111" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A112" s="9">
-        <v>46223</v>
-      </c>
-      <c r="B112" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A113" s="9">
-        <v>46224</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D113" s="10"/>
-    </row>
-    <row r="114" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A114" s="9">
-        <v>46225</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A115" s="9">
-        <v>46226</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="9">
-        <v>46227</v>
-      </c>
-      <c r="B116" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="9">
-        <v>46228</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A118" s="9">
-        <v>46229</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A119" s="9">
-        <v>46230</v>
-      </c>
-      <c r="B119" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D119" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A120" s="9">
-        <v>46231</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A121" s="9">
-        <v>46232</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D121" s="10"/>
+      <c r="D121" s="11"/>
+    </row>
+    <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D122" s="12"/>
+    </row>
+    <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="D123" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:C123" xr:uid="{E1FB5C3E-D482-484D-8C71-32C481BF75DA}"/>
-  <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{73965210-AF45-434C-9997-EC4B858A4516}"/>
-    <hyperlink ref="D13" r:id="rId2" xr:uid="{2EC4AA29-8667-4F84-B863-E12F9B084B44}"/>
-    <hyperlink ref="D21" r:id="rId3" xr:uid="{DDD0733A-C40D-4D69-B665-B30AC3905495}"/>
-    <hyperlink ref="D29" r:id="rId4" xr:uid="{F612D8E7-14B3-4399-8D85-AE62FC872E0E}"/>
-    <hyperlink ref="D37" r:id="rId5" xr:uid="{26E9E5BB-55EE-45F3-85A2-F0B8242537E8}"/>
-    <hyperlink ref="D45" r:id="rId6" xr:uid="{EE20484F-9F2C-42FA-A3FD-49FF2377B553}"/>
-    <hyperlink ref="D53" r:id="rId7" xr:uid="{EB3A445B-F0B1-4834-B366-B7987C8BC0AD}"/>
-    <hyperlink ref="D64" r:id="rId8" xr:uid="{945E9506-F6A7-4019-B526-725709DEE254}"/>
-    <hyperlink ref="D69" r:id="rId9" xr:uid="{65E026CE-5919-4DBC-AE06-D8AF53630533}"/>
-    <hyperlink ref="D77" r:id="rId10" xr:uid="{54482943-3E2C-4A82-BB56-0944C6FC9E59}"/>
-    <hyperlink ref="D85" r:id="rId11" xr:uid="{E28CDF9E-7B4B-44E7-A827-AB25D9D857D0}"/>
-    <hyperlink ref="D93" r:id="rId12" xr:uid="{F69F5627-AF07-4ADB-A700-9EF54169BED1}"/>
-    <hyperlink ref="D101" r:id="rId13" xr:uid="{54F77405-0341-4E3B-A268-55EA74B9E5BE}"/>
-    <hyperlink ref="D109" r:id="rId14" xr:uid="{A91F524B-B019-42C3-BC71-79B11E333872}"/>
-    <hyperlink ref="D117" r:id="rId15" xr:uid="{140EBCD1-6BA3-4EC8-B081-B5D598787657}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="17" orientation="portrait" r:id="rId16"/>
+  <pageSetup paperSize="17" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A273B510-D8E7-43C9-846D-8D43264FA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E08306-EBAD-4BC2-87F1-B931F0FF2137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="22">
   <si>
     <t>Date</t>
   </si>
@@ -104,9 +104,6 @@
   </si>
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>mahfuja.toma@oculintech.com</t>
   </si>
   <si>
     <t>topu.rajbongshi@oculintech.com</t>
@@ -643,9 +640,7 @@
       <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -748,9 +743,7 @@
       <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
@@ -943,9 +936,7 @@
       <c r="C28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
@@ -1042,9 +1033,7 @@
       <c r="C36" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -1141,9 +1130,7 @@
       <c r="C44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D44" s="11"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
@@ -1240,9 +1227,7 @@
       <c r="C52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D52" s="11"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
@@ -1317,9 +1302,7 @@
       <c r="C58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D58" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D58" s="11"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
@@ -1354,9 +1337,7 @@
       <c r="C61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D61" s="11"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
@@ -1442,9 +1423,7 @@
       <c r="C68" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D68" s="11"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
@@ -1544,9 +1523,7 @@
       <c r="C76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D76" s="11"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
@@ -1646,9 +1623,7 @@
       <c r="C84" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D84" s="11"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
@@ -1748,9 +1723,7 @@
       <c r="C92" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D92" s="11"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
@@ -1850,9 +1823,7 @@
       <c r="C100" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D100" s="11"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
@@ -1952,9 +1923,7 @@
       <c r="C108" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D108" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D108" s="11"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
@@ -2054,9 +2023,7 @@
       <c r="C116" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D116" s="11" t="s">
-        <v>22</v>
-      </c>
+      <c r="D116" s="11"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="7">

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E08306-EBAD-4BC2-87F1-B931F0FF2137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DB2B82-657A-4D4F-A915-9F0989F4988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -106,14 +106,14 @@
     <t>Email</t>
   </si>
   <si>
-    <t>topu.rajbongshi@oculintech.com</t>
+    <t>mahfuja.toma@oculintech.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +152,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -205,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -241,6 +248,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -681,7 +691,7 @@
       <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -767,7 +777,7 @@
       <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -877,7 +887,7 @@
       <c r="C23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -974,7 +984,7 @@
       <c r="C31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1071,7 +1081,7 @@
       <c r="C39" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1168,7 +1178,7 @@
       <c r="C47" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1265,7 +1275,7 @@
       <c r="C55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1361,7 +1371,7 @@
       <c r="C63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="D63" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1461,7 +1471,7 @@
       <c r="C71" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1561,7 +1571,7 @@
       <c r="C79" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="9" t="s">
+      <c r="D79" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1661,7 +1671,7 @@
       <c r="C87" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D87" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1761,7 +1771,7 @@
       <c r="C95" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="9" t="s">
+      <c r="D95" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1861,7 +1871,7 @@
       <c r="C103" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D103" s="9" t="s">
+      <c r="D103" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1961,7 +1971,7 @@
       <c r="C111" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D111" s="9" t="s">
+      <c r="D111" s="13" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2061,7 +2071,7 @@
       <c r="C119" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D119" s="9" t="s">
+      <c r="D119" s="13" t="s">
         <v>21</v>
       </c>
     </row>

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DB2B82-657A-4D4F-A915-9F0989F4988B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E9EB04-EB20-42BB-AD26-EA16B8B611AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -108,12 +108,30 @@
   <si>
     <t>mahfuja.toma@oculintech.com</t>
   </si>
+  <si>
+    <t>bithi.bhowmik@oculintech.com</t>
+  </si>
+  <si>
+    <t>kaniz.fatema@oculintech.com</t>
+  </si>
+  <si>
+    <t>afroja.jahan@oculintech.com</t>
+  </si>
+  <si>
+    <t>mominul.islam@oculintech.com</t>
+  </si>
+  <si>
+    <t>nurnaher.aktar@oculintech.com</t>
+  </si>
+  <si>
+    <t>topu.rajbongshi@oculintech.com</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,21 +155,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -208,11 +211,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -235,27 +237,20 @@
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -594,7 +589,7 @@
     <col min="1" max="1" width="17.44140625" customWidth="1"/>
     <col min="2" max="2" width="18.109375" customWidth="1"/>
     <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="32.21875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" style="8" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.5546875" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" customWidth="1"/>
@@ -611,7 +606,7 @@
       <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="6"/>
@@ -628,6 +623,9 @@
       <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D2" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
@@ -639,6 +637,9 @@
       <c r="C3" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D3" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
@@ -650,7 +651,9 @@
       <c r="C4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -662,7 +665,9 @@
       <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
@@ -674,8 +679,8 @@
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>19</v>
+      <c r="D6" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="J6" t="s">
         <v>18</v>
@@ -691,7 +696,7 @@
       <c r="C7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -705,6 +710,9 @@
       <c r="C8" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D8" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -716,8 +724,8 @@
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>19</v>
+      <c r="D9" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -730,6 +738,9 @@
       <c r="C10" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D10" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -741,7 +752,9 @@
       <c r="C11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
@@ -753,7 +766,9 @@
       <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
@@ -765,7 +780,9 @@
       <c r="C13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
@@ -777,7 +794,7 @@
       <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -791,8 +808,8 @@
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>19</v>
+      <c r="D15" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -805,6 +822,9 @@
       <c r="C16" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D16" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
@@ -816,7 +836,9 @@
       <c r="C17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
@@ -828,6 +850,9 @@
       <c r="C18" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D18" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
@@ -839,6 +864,9 @@
       <c r="C19" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D19" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
@@ -850,6 +878,9 @@
       <c r="C20" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D20" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
@@ -861,7 +892,9 @@
       <c r="C21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
@@ -873,8 +906,8 @@
       <c r="C22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>19</v>
+      <c r="D22" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -887,7 +920,7 @@
       <c r="C23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -901,6 +934,9 @@
       <c r="C24" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D24" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
@@ -912,7 +948,9 @@
       <c r="C25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
@@ -924,6 +962,9 @@
       <c r="C26" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D26" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
@@ -935,6 +976,9 @@
       <c r="C27" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D27" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
@@ -946,7 +990,9 @@
       <c r="C28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
@@ -958,7 +1004,9 @@
       <c r="C29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="8"/>
+      <c r="D29" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
@@ -970,8 +1018,8 @@
       <c r="C30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>19</v>
+      <c r="D30" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -984,7 +1032,7 @@
       <c r="C31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -998,6 +1046,9 @@
       <c r="C32" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D32" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -1009,7 +1060,9 @@
       <c r="C33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="11"/>
+      <c r="D33" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -1021,6 +1074,9 @@
       <c r="C34" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D34" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
@@ -1032,6 +1088,9 @@
       <c r="C35" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D35" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
@@ -1043,7 +1102,9 @@
       <c r="C36" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="11"/>
+      <c r="D36" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -1055,7 +1116,9 @@
       <c r="C37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="8"/>
+      <c r="D37" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -1067,8 +1130,8 @@
       <c r="C38" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>19</v>
+      <c r="D38" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1081,7 +1144,7 @@
       <c r="C39" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1095,6 +1158,9 @@
       <c r="C40" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D40" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
@@ -1106,7 +1172,9 @@
       <c r="C41" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D41" s="11"/>
+      <c r="D41" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
@@ -1118,6 +1186,9 @@
       <c r="C42" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D42" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
@@ -1129,6 +1200,9 @@
       <c r="C43" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D43" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
@@ -1140,7 +1214,9 @@
       <c r="C44" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="11"/>
+      <c r="D44" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
@@ -1152,7 +1228,9 @@
       <c r="C45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="8"/>
+      <c r="D45" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
@@ -1164,8 +1242,8 @@
       <c r="C46" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>19</v>
+      <c r="D46" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1178,7 +1256,7 @@
       <c r="C47" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1192,6 +1270,9 @@
       <c r="C48" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D48" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
@@ -1203,7 +1284,9 @@
       <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="11"/>
+      <c r="D49" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
@@ -1215,6 +1298,9 @@
       <c r="C50" s="6" t="s">
         <v>4</v>
       </c>
+      <c r="D50" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
@@ -1226,6 +1312,9 @@
       <c r="C51" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="D51" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
@@ -1237,7 +1326,9 @@
       <c r="C52" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="11"/>
+      <c r="D52" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
@@ -1249,7 +1340,9 @@
       <c r="C53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="8"/>
+      <c r="D53" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
@@ -1261,8 +1354,8 @@
       <c r="C54" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>19</v>
+      <c r="D54" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1275,7 +1368,7 @@
       <c r="C55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1289,6 +1382,9 @@
       <c r="C56" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D56" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
@@ -1300,7 +1396,9 @@
       <c r="C57" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="11"/>
+      <c r="D57" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
@@ -1312,7 +1410,9 @@
       <c r="C58" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D58" s="11"/>
+      <c r="D58" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
@@ -1324,6 +1424,9 @@
       <c r="C59" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D59" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
@@ -1335,7 +1438,9 @@
       <c r="C60" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="11"/>
+      <c r="D60" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
@@ -1347,7 +1452,9 @@
       <c r="C61" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="11"/>
+      <c r="D61" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
@@ -1359,7 +1466,9 @@
       <c r="C62" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="12"/>
+      <c r="D62" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
@@ -1371,7 +1480,7 @@
       <c r="C63" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1385,7 +1494,9 @@
       <c r="C64" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D64" s="8"/>
+      <c r="D64" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
@@ -1397,7 +1508,9 @@
       <c r="C65" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D65" s="11"/>
+      <c r="D65" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
@@ -1409,7 +1522,9 @@
       <c r="C66" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="12"/>
+      <c r="D66" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
@@ -1421,7 +1536,9 @@
       <c r="C67" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D67" s="12"/>
+      <c r="D67" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
@@ -1433,7 +1550,9 @@
       <c r="C68" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="11"/>
+      <c r="D68" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
@@ -1445,7 +1564,9 @@
       <c r="C69" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D69" s="8"/>
+      <c r="D69" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
@@ -1457,8 +1578,8 @@
       <c r="C70" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>19</v>
+      <c r="D70" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1471,7 +1592,7 @@
       <c r="C71" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1485,7 +1606,9 @@
       <c r="C72" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="12"/>
+      <c r="D72" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
@@ -1497,7 +1620,9 @@
       <c r="C73" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="11"/>
+      <c r="D73" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
@@ -1509,7 +1634,9 @@
       <c r="C74" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="12"/>
+      <c r="D74" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
@@ -1521,7 +1648,9 @@
       <c r="C75" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D75" s="12"/>
+      <c r="D75" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
@@ -1533,7 +1662,9 @@
       <c r="C76" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="11"/>
+      <c r="D76" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
@@ -1545,7 +1676,9 @@
       <c r="C77" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D77" s="8"/>
+      <c r="D77" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
@@ -1557,8 +1690,8 @@
       <c r="C78" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="11" t="s">
-        <v>19</v>
+      <c r="D78" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,7 +1704,7 @@
       <c r="C79" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1585,7 +1718,9 @@
       <c r="C80" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="12"/>
+      <c r="D80" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
@@ -1597,7 +1732,9 @@
       <c r="C81" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D81" s="11"/>
+      <c r="D81" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
@@ -1609,7 +1746,9 @@
       <c r="C82" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D82" s="12"/>
+      <c r="D82" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
@@ -1621,7 +1760,9 @@
       <c r="C83" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D83" s="12"/>
+      <c r="D83" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
@@ -1633,7 +1774,9 @@
       <c r="C84" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="11"/>
+      <c r="D84" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
@@ -1645,7 +1788,9 @@
       <c r="C85" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="8"/>
+      <c r="D85" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
@@ -1657,8 +1802,8 @@
       <c r="C86" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D86" s="11" t="s">
-        <v>19</v>
+      <c r="D86" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -1671,7 +1816,7 @@
       <c r="C87" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1685,7 +1830,9 @@
       <c r="C88" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D88" s="12"/>
+      <c r="D88" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
@@ -1697,7 +1844,9 @@
       <c r="C89" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D89" s="11"/>
+      <c r="D89" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
@@ -1709,7 +1858,9 @@
       <c r="C90" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="12"/>
+      <c r="D90" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
@@ -1721,7 +1872,9 @@
       <c r="C91" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D91" s="12"/>
+      <c r="D91" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
@@ -1733,7 +1886,9 @@
       <c r="C92" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D92" s="11"/>
+      <c r="D92" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
@@ -1745,7 +1900,9 @@
       <c r="C93" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D93" s="8"/>
+      <c r="D93" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
@@ -1757,8 +1914,8 @@
       <c r="C94" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D94" s="11" t="s">
-        <v>19</v>
+      <c r="D94" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -1771,7 +1928,7 @@
       <c r="C95" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D95" s="13" t="s">
+      <c r="D95" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1785,7 +1942,9 @@
       <c r="C96" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D96" s="12"/>
+      <c r="D96" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
@@ -1797,7 +1956,9 @@
       <c r="C97" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D97" s="11"/>
+      <c r="D97" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
@@ -1809,7 +1970,9 @@
       <c r="C98" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="12"/>
+      <c r="D98" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
@@ -1821,7 +1984,9 @@
       <c r="C99" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D99" s="12"/>
+      <c r="D99" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
@@ -1833,7 +1998,9 @@
       <c r="C100" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="11"/>
+      <c r="D100" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
@@ -1845,7 +2012,9 @@
       <c r="C101" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D101" s="8"/>
+      <c r="D101" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
@@ -1857,8 +2026,8 @@
       <c r="C102" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D102" s="11" t="s">
-        <v>19</v>
+      <c r="D102" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -1871,7 +2040,7 @@
       <c r="C103" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1885,7 +2054,9 @@
       <c r="C104" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D104" s="12"/>
+      <c r="D104" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
@@ -1897,7 +2068,9 @@
       <c r="C105" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D105" s="11"/>
+      <c r="D105" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
@@ -1909,7 +2082,9 @@
       <c r="C106" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="12"/>
+      <c r="D106" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
@@ -1921,7 +2096,9 @@
       <c r="C107" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D107" s="12"/>
+      <c r="D107" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
@@ -1933,7 +2110,9 @@
       <c r="C108" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D108" s="11"/>
+      <c r="D108" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
@@ -1945,7 +2124,9 @@
       <c r="C109" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D109" s="8"/>
+      <c r="D109" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
@@ -1957,8 +2138,8 @@
       <c r="C110" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D110" s="11" t="s">
-        <v>19</v>
+      <c r="D110" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -1971,7 +2152,7 @@
       <c r="C111" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D111" s="13" t="s">
+      <c r="D111" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1985,7 +2166,9 @@
       <c r="C112" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D112" s="12"/>
+      <c r="D112" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
@@ -1997,7 +2180,9 @@
       <c r="C113" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D113" s="11"/>
+      <c r="D113" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
@@ -2009,7 +2194,9 @@
       <c r="C114" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="12"/>
+      <c r="D114" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
@@ -2021,7 +2208,9 @@
       <c r="C115" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D115" s="12"/>
+      <c r="D115" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
@@ -2033,7 +2222,9 @@
       <c r="C116" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D116" s="11"/>
+      <c r="D116" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
@@ -2045,7 +2236,9 @@
       <c r="C117" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D117" s="8"/>
+      <c r="D117" s="11" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
@@ -2057,8 +2250,8 @@
       <c r="C118" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D118" s="11" t="s">
-        <v>19</v>
+      <c r="D118" s="8" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -2071,7 +2264,7 @@
       <c r="C119" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2085,7 +2278,9 @@
       <c r="C120" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D120" s="12"/>
+      <c r="D120" s="8" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
@@ -2097,13 +2292,15 @@
       <c r="C121" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D121" s="11"/>
+      <c r="D121" s="8" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="122" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D122" s="12"/>
+      <c r="D122" s="9"/>
     </row>
     <row r="123" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="D123" s="12"/>
+      <c r="D123" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:C123" xr:uid="{E1FB5C3E-D482-484D-8C71-32C481BF75DA}"/>

--- a/RoasterList.xlsx
+++ b/RoasterList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\All Projects\CMS-GIT\RoasterAlert\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\DPDC Stuff\CMS-GIT\RoasterAlert\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E9EB04-EB20-42BB-AD26-EA16B8B611AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A971F7A-A1B0-4715-BE1B-6E8ECC2E8612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D1ADB46A-FEE1-453A-9125-EB62AA815D9C}"/>
   </bookViews>
